--- a/output/体测工作簿_2024-2025-1_初一_1班.xlsx
+++ b/output/体测工作簿_2024-2025-1_初一_1班.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筛选说明和校验摘要" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学生成绩" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总分排名" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未达标名单" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补测名单" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班级统计" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校验_重复学号" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校验_项目缺失" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补测原因汇总" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班级统计" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校验_重复学号" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校验_项目缺失" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,16 +421,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -438,10 +444,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>基本信息</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>学期</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2024-2025-1</t>
         </is>
@@ -450,10 +461,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>基本信息</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>年级</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>初一</t>
         </is>
@@ -462,165 +478,359 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>基本信息</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>筛选条件</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>班级=1班</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>基本信息</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>学生范围</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>共 15 名学生</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>总人数</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>15</v>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>已完成（全部达标）</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
+          <t>学生状态</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>总人数</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>部分缺项</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
+          <t>学生状态</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>已完成（全部达标）</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>完全缺考</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
+          <t>学生状态</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>部分缺项</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>单项不及格</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>12</v>
+          <t>学生状态</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>完全缺考</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>学生状态</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>学生状态</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>完成率(%)</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C12" t="n">
         <v>13.3</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>参评人数</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>平均分</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>74.7</v>
+          <t>成绩统计</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>参评人数</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>最高分</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>89.5</v>
+          <t>成绩统计</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>平均分</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>74.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>最低分</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>59</v>
+          <t>成绩统计</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>最高分</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>89.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>及格率(%)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>93.3</v>
+          <t>成绩统计</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>最低分</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>良好率(%)</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>20</v>
+          <t>成绩统计</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>及格率(%)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>93.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>成绩统计</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>良好率(%)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>成绩统计</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>优秀率(%)</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="C20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>待补测人数</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>补测情况</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>待补测总人数</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>补测情况</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>完全缺考</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>补测情况</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>部分缺项</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>补测情况</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>校验问题</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>问题总数</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>校验问题</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>校验_重复学号</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>校验问题</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>校验_项目缺失</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2 条</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +3034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2878,6 +3088,11 @@
           <t>补测原因</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>原因分类</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2924,6 +3139,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 50米跑(不及格(50分)), 坐位体前屈(不及格(50分)), 1000米跑(男)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2970,6 +3190,11 @@
           <t>立定跳远(不及格(50分)), 引体向上(男)(不及格(50分)), 1000米跑(男)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3016,6 +3241,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分)), 800米跑(女)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3062,6 +3292,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 坐位体前屈(不及格(50分))</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3108,6 +3343,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 仰卧起坐(女)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3154,6 +3394,11 @@
           <t>50米跑(缺考), 仰卧起坐(女)(不及格(50分))</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>部分缺项</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3200,6 +3445,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 50米跑(不及格(50分))</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3246,6 +3496,11 @@
           <t>身高体重指数(BMI)(不及格(50分)), 50米跑(不及格(50分))</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3292,6 +3547,11 @@
           <t>立定跳远(不及格(50分))</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3338,6 +3598,11 @@
           <t>坐位体前屈(不及格(30分))</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3384,6 +3649,11 @@
           <t>坐位体前屈(不及格(50分))</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3430,6 +3700,11 @@
           <t>肺活量(不及格(50分))</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3474,6 +3749,11 @@
       <c r="J14" t="inlineStr">
         <is>
           <t>1000米跑(男)(不及格(50分))</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
         </is>
       </c>
     </row>
@@ -3488,93 +3768,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>排名</t>
+          <t>分类</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>班级</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>学生人数</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>平均分</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>最高分</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>最低分</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>优秀率(%)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>良好率(%)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>及格率(%)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>不及格率(%)</t>
+          <t>人数</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>待补测总人数</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>完全缺考</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>部分缺项</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1班</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D2" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>59</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I2" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6.7</v>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>单项不及格</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【按项目原始缺项】</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  50米跑</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【按项目单项不及格】</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  身高体重指数(BMI)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  坐位体前屈</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1000米跑(男)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  50米跑</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  立定跳远</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  仰卧起坐(女)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  引体向上(男)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  肺活量</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  800米跑(女)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3588,201 +3958,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>student_id</t>
+          <t>排名</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>班级</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>学生人数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>class_name</t>
+          <t>平均分</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>grade</t>
+          <t>最高分</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>height</t>
+          <t>最低分</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>优秀率(%)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>vital_capacity</t>
+          <t>良好率(%)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>run_50m</t>
+          <t>及格率(%)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>standing_jump</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>sit_and_reach</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>pull_up</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>run_1000m</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>sit_up</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>run_800m</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>bmi</t>
+          <t>不及格率(%)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C2024001</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>学生001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1班</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
+          <t>1班</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>89.5</v>
       </c>
       <c r="F2" t="n">
-        <v>150.8</v>
+        <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2914</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>73.3</v>
       </c>
       <c r="J2" t="n">
-        <v>153</v>
-      </c>
-      <c r="K2" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>327</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>22.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>C2024001</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>学生021</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>男</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2班</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>171.7</v>
-      </c>
-      <c r="G3" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4360</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>240</v>
-      </c>
-      <c r="K3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L3" t="n">
-        <v>13</v>
-      </c>
-      <c r="M3" t="n">
-        <v>186</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>25.5</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -3796,6 +4058,214 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>student_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>class_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>vital_capacity</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>run_50m</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>standing_jump</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>sit_and_reach</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pull_up</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>run_1000m</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>sit_up</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>run_800m</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>bmi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C2024001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>学生001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1班</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>150.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2914</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>153</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>327</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C2024001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>学生021</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2班</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>171.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4360</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>240</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M3" t="n">
+        <v>186</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
